--- a/AAII_Financials/Quarterly/SMSMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SMSMY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="92">
   <si>
     <t>SMSMY</t>
   </si>
@@ -656,24 +656,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -684,103 +684,111 @@
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -823,47 +831,53 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S8" s="3">
         <v>1637300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1425700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1795900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2190900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2288700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2481900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2310900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1994300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1585400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1510800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1711400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>4591700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2446900</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -906,47 +920,53 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S9" s="3">
         <v>1390600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1239200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1574100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1892400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2001800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2161000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1973200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1698300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1348000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1250600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1487300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>4027100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2154800</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -989,47 +1009,53 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
         <v>246700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>186500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>221800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>298500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>286800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>320900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>337700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>296000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>237400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>260200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>224100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>564600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>292100</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1059,8 +1085,10 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1142,8 +1170,14 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1225,8 +1259,14 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1269,47 +1309,53 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>-8300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>26100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>18300</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>-7200</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>121800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>-700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1352,47 +1398,53 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="3">
         <v>65700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>67700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>64900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>45600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>44000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>43600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>43600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>41700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>37100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>40500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>46800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>87700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>42200</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1419,8 +1471,10 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1463,47 +1517,53 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="3">
         <v>1620800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1546100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1876100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2143600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2252300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2410700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2244600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1941500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1552000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1490900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1900100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>4523000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2399600</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1546,47 +1606,53 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="3">
         <v>16500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-120400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-80300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>47300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>36400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>71300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>66300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>52800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>33400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>19900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-188700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>68600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1616,8 +1682,10 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1660,47 +1728,53 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="3">
         <v>34800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>26100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>13800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>27000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>36300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>37100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>25200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>20000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>27900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>8200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>30800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>22100</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1743,47 +1817,53 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3">
         <v>116900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-90000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-1500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>77400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>116700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>111700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>135000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>73200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>98400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>16100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-133600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>187100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>111700</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1826,21 +1906,21 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
         <v>2500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>2900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>1500</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1853,11 +1933,11 @@
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1865,8 +1945,14 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1909,47 +1995,53 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="3">
         <v>48800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-97200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-68000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>74300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>72700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>108300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>91500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>72800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>61300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>20100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-180500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>99400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1992,47 +2084,53 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="3">
         <v>13500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>21600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-9100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>21000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>20200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>30300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>20500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-18500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>8200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>19700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2114,8 +2212,14 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2158,47 +2262,53 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="3">
         <v>35300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-118800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-58900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>53300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>52400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>78000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>70900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>91300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>53100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>22600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-176900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>79700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>57200</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2241,47 +2351,53 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S27" s="3">
         <v>35300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-118800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-58900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>53300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>52400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>78000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>70900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>91300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>53100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>22600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-176900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>79700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>57200</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2363,8 +2479,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2410,44 +2532,50 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3">
         <v>6100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>-1400</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>-3000</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>1900</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2529,8 +2657,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2612,8 +2746,14 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2656,47 +2796,53 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S32" s="3">
         <v>-34800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-26100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-13800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-27000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-36300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-37100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-25200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-27900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-8200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-30800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-22100</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2739,47 +2885,53 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S33" s="3">
         <v>35300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-112700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-60300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>50400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>52400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>80000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>70900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>91300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>53100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>22600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-176900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>79700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2861,8 +3013,14 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2905,135 +3063,147 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S35" s="3">
         <v>35300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-112700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-60300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>50400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>52400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>80000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>70900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>91300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>53100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>22600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-176900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>79700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3063,8 +3233,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3094,755 +3266,811 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>122800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>121800</v>
+      </c>
+      <c r="F41" s="3">
         <v>70800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>70200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>118700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>112900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>124500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>139400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>62100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>60700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>142600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>135000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>205500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>207000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>263500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>206200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>147100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>147500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>253400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>148100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>242100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>305300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>279600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>210700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>167100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>269400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>229300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>48100</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E42" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F42" s="3">
         <v>14300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>14200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>12900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>12300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>25900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>29000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>13900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>13600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>9800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>9300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>14000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>14100</v>
-      </c>
-      <c r="P42" s="3">
-        <v>13300</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>15200</v>
       </c>
       <c r="R42" s="3">
         <v>13300</v>
       </c>
       <c r="S42" s="3">
+        <v>15200</v>
+      </c>
+      <c r="T42" s="3">
+        <v>13300</v>
+      </c>
+      <c r="U42" s="3">
         <v>16100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>11600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>10200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>13500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>12000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>10000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>8300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>7800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>8700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>11200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>597300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>592600</v>
+      </c>
+      <c r="F43" s="3">
         <v>505300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>501000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>551500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>524600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>459700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>515100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>413300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>404000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>524300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>496300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>448500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>451900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>408400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>265300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>253800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>313600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>255900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>332700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>329700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>267800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>312400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>273000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>267800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>217300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>287800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>278300</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>424800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>421500</v>
+      </c>
+      <c r="F44" s="3">
         <v>377100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>373900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>331900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>315800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>346800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>388500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>402800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>393700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>485300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>459400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>470900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>474500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>410900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>226700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>216300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>215300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>293000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>361700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>404800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>408000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>297400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>256800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>268100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>248000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>345700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>437700</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>39100</v>
+      </c>
+      <c r="F45" s="3">
         <v>21100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>20900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>8100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>7700</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>499900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>488600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>65200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>61700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>138200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>139300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>74900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>4700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>7300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>2800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>16600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>19400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1222300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1212600</v>
+      </c>
+      <c r="F46" s="3">
         <v>1006000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>997600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1043500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>992700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>956900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1072000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1414900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1382900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1227200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1161700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1305400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1315200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1171000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>713500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>630700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>692500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>813900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>854100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>991600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>997800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>906800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>751700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>727300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>762800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>875200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>814600</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>529600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>525400</v>
+      </c>
+      <c r="F47" s="3">
         <v>500600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>496400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>431100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>410100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>460100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>515500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>390200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>381400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>467100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>442200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>399200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>402200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>476400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>280900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>283300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>243200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>218900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>211800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>202800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>182400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>158700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>144100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>138800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>140200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>226200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>263200</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1150800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1141700</v>
+      </c>
+      <c r="F48" s="3">
         <v>1096300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1087000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1099000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1045500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1044600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1170400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1087300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1062700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1284900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1216300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1163200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1171900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1129300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>907800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>973200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1035000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>838500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>833800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>825200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>771500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>717100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>674800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>663000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>710500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>748700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>710600</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>228800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>227000</v>
+      </c>
+      <c r="F49" s="3">
         <v>171100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>169700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>174800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>166300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>190000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>212900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>201000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>196500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>169100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>160000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>98500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>99200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>90300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>61700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>38800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>71500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>128200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>136700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>141800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>123400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>117000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>109500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>114300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>124700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>166300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>165400</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3924,8 +4152,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4007,91 +4241,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F52" s="3">
         <v>1000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>8600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>8200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>10300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>10000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>18900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>19000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>133700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>148300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>169300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>108300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>108100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>124600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>110500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>126400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>82200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>86800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>78400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>74600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>67600</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4173,91 +4419,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3280900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3254800</v>
+      </c>
+      <c r="F54" s="3">
         <v>2892900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2868600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2914900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2772900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2765700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>3098600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3272400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>3198400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>3247200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3073900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3131900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>3155400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2958100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2097600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2074300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2211500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2107800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2144500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2286100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2185700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2026000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1762300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1730200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1816500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>2091000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>2021400</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4287,8 +4545,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4318,506 +4578,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>283600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>281400</v>
+      </c>
+      <c r="F57" s="3">
         <v>427100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>423500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>202500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>192700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>417800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>468100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>242800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>237300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>550800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>521400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>313600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>316000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>413000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>273400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>238900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>265600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>354700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>371200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>460600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>413000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>338800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>309100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>291300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>282400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>382900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>347900</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>50300</v>
+      </c>
+      <c r="F58" s="3">
         <v>52200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>51700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>49800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>47300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>47600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>53300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>49000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>47900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>57000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>53900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>54600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>55100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>53400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>62700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>45600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>88000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>364900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>362000</v>
+      </c>
+      <c r="F59" s="3">
         <v>185800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>184200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>289300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>275200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>151800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>170100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>598100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>584500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>131600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>124600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>318700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>321100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>101600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>62400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>62000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>56700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>81100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>58100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>105500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>71100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>98100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>54300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>62800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>46500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>56500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>78200</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>801500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>795100</v>
+      </c>
+      <c r="F60" s="3">
         <v>665000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>659400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>627000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>596500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>617200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>691500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>953600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>932100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>739400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>699900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>727800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>733300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>568100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>398500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>346500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>410300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>435900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>429800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>567200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>485800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>438400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>365100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>355500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>330500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>439700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>426400</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>521200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>517100</v>
+      </c>
+      <c r="F61" s="3">
         <v>431500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>427900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>466700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>443900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>319600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>358100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>474300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>463600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>553800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>524200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>481000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>484600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>473200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>255700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>265200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>193700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>23300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>42400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>28100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>3000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>4000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F62" s="3">
         <v>20400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>20200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>8900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>8500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>23800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>26700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>7000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>6800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>47900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>45400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>36600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>36900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>69100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>160800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>180100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>173800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>127600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>125300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>128000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>124900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>131800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>137400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>138600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>141100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>117100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>105600</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4899,8 +5197,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4982,8 +5286,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5065,91 +5375,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1443700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1432200</v>
+      </c>
+      <c r="F66" s="3">
         <v>1226900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1216500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1219000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1159600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1071000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1199900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1562600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1527200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1444600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1367600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1363700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1374000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1216700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>815000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>791800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>777800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>586700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>597500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>723400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>612500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>572700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>505500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>496900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>475600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>558000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>544100</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5179,8 +5501,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5262,8 +5586,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5345,8 +5675,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5428,8 +5764,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5511,91 +5853,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-250800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-248800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-407600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-404200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-358200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-340700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-308200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-345300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-319300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-312100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-241900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-229000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-232300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-234000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-268200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-484800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-505200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-399700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-307100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-342900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-372600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-471500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-480400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-510300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-556600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-595400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-496700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-551900</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5677,8 +6031,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5760,8 +6120,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5843,91 +6209,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1837200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1822600</v>
+      </c>
+      <c r="F76" s="3">
         <v>1666100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1652100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1695900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1613300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1694700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1898700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1709800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1671100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1802600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1706400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1768200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1781500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1741500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1282600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1282500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1433700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1521000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1547000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1562700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1573200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1453300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1256900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1233300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1340900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1533000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1477200</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6009,96 +6387,108 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6141,47 +6531,53 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S81" s="3">
         <v>35300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-112700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-60300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>50400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>52400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>80000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>70900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>91300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>53100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>22600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-176900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>79700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6211,56 +6607,58 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3">
         <v>36600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>41000</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3">
         <v>35200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>33300</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>35500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>33700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>34500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>37600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>36400</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -6294,8 +6692,14 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6377,8 +6781,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6460,8 +6870,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6543,8 +6959,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6626,8 +7048,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6709,91 +7137,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>92100</v>
+      </c>
+      <c r="F89" s="3">
         <v>51800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>51300</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3">
         <v>107600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>120600</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N89" s="3">
         <v>34700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>32800</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R89" s="3">
         <v>109400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>99500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-20200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-22600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>225000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>13700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>86300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>101700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>112600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>75600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>98500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>216300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>38500</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6823,91 +7263,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-47400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-22200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-22000</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3">
         <v>-25800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-28900</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N91" s="3">
         <v>-31700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-30000</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R91" s="3">
         <v>-42900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-44400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-60500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-80000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-74500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-57900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-65300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-65600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-43300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-45100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-43500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-31300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-69100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-28800</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6989,8 +7437,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7072,91 +7526,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-21100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-21000</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3">
         <v>12900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>14400</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" s="3">
         <v>-74700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-70800</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3">
         <v>-33200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-36600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>31300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-50800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-68000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-62600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-131400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-60800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-37400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-37500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-28400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>30300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-21500</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7186,91 +7652,99 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E96" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F96" s="3">
         <v>8400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>8300</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
         <v>6000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>6700</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3">
         <v>13800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>13100</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3">
         <v>32800</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-7800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-25500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-30800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-42000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-33200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-46700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-29200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-13500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-18900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-38600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-14900</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7352,8 +7826,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7435,8 +7915,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7518,253 +8004,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-54900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-54400</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3">
         <v>-88400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-99000</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" s="3">
         <v>5700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>5400</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R100" s="3">
         <v>-29600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-2900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-7700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-37100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-48200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-40100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-28800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-25500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-21900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-44400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-32300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-72900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-13900</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3">
         <v>1300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>1500</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3">
         <v>-800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-1100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-5300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>4600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>1500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>4700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>5500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>8000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>14100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>24500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-25000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-24800</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>33400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>37400</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-33900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-32100</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>45800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>54700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>2800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-105900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>110400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-84300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-39100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>11900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>45000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>46000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-89200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>45800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>187800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>6600</v>
       </c>
     </row>
